--- a/gstdatabase/GSTR-3B-2017-2018.xlsx
+++ b/gstdatabase/GSTR-3B-2017-2018.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05970A36-801F-4225-8CE4-9CB02EDC7BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EC4840-13CB-42A0-9EC0-794621CD4DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="Y11" s="15">
         <f t="shared" ref="Y11:Y48" si="8">Z11-X11</f>
-        <v>21007</v>
+        <v>21008</v>
       </c>
       <c r="Z11" s="13">
-        <v>56388</v>
+        <v>56389</v>
       </c>
       <c r="AA11" s="14">
         <f t="shared" ref="AA11:AA48" si="9">Z11/W11</f>
-        <v>0.9408820143164639</v>
+        <v>0.94089870017186428</v>
       </c>
       <c r="AB11" s="12">
         <v>60956</v>
@@ -2139,14 +2139,14 @@
       </c>
       <c r="Y16" s="15">
         <f t="shared" si="8"/>
-        <v>169636</v>
+        <v>169637</v>
       </c>
       <c r="Z16" s="13">
-        <v>526220</v>
+        <v>526221</v>
       </c>
       <c r="AA16" s="14">
         <f t="shared" si="9"/>
-        <v>0.96293869962468415</v>
+        <v>0.96294052954125819</v>
       </c>
       <c r="AB16" s="12">
         <v>558644</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="O17" s="15">
         <f t="shared" si="4"/>
-        <v>200006</v>
+        <v>200007</v>
       </c>
       <c r="P17" s="13">
-        <v>425348</v>
+        <v>425349</v>
       </c>
       <c r="Q17" s="14">
         <f t="shared" si="5"/>
-        <v>0.97572769877663568</v>
+        <v>0.97572999272817362</v>
       </c>
       <c r="R17" s="12">
         <v>418736</v>
@@ -2368,14 +2368,14 @@
       </c>
       <c r="AS17" s="15">
         <f t="shared" si="16"/>
-        <v>143473</v>
+        <v>143474</v>
       </c>
       <c r="AT17" s="13">
-        <v>434565</v>
+        <v>434566</v>
       </c>
       <c r="AU17" s="14">
         <f t="shared" si="17"/>
-        <v>0.95322545619657417</v>
+        <v>0.95322764971297835</v>
       </c>
     </row>
     <row r="18" spans="1:47" x14ac:dyDescent="0.3">
@@ -2427,14 +2427,14 @@
       </c>
       <c r="O18" s="15">
         <f t="shared" si="4"/>
-        <v>403670</v>
+        <v>403671</v>
       </c>
       <c r="P18" s="13">
-        <v>850385</v>
+        <v>850386</v>
       </c>
       <c r="Q18" s="14">
         <f t="shared" si="5"/>
-        <v>0.95779608404966576</v>
+        <v>0.95779721035843646</v>
       </c>
       <c r="R18" s="12">
         <v>809536</v>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="AD18" s="15">
         <f t="shared" si="10"/>
-        <v>171869</v>
+        <v>171870</v>
       </c>
       <c r="AE18" s="22">
-        <v>793323</v>
+        <v>793324</v>
       </c>
       <c r="AF18" s="14">
         <f t="shared" si="11"/>
-        <v>0.9360610823209583</v>
+        <v>0.93606226224525435</v>
       </c>
       <c r="AG18" s="12">
         <v>871836</v>
@@ -2529,14 +2529,14 @@
       </c>
       <c r="AS18" s="15">
         <f t="shared" si="16"/>
-        <v>225453</v>
+        <v>225455</v>
       </c>
       <c r="AT18" s="13">
-        <v>845573</v>
+        <v>845575</v>
       </c>
       <c r="AU18" s="14">
         <f t="shared" si="17"/>
-        <v>0.92598660255223897</v>
+        <v>0.92598879275131718</v>
       </c>
     </row>
     <row r="19" spans="1:47" x14ac:dyDescent="0.3">
@@ -2588,14 +2588,14 @@
       </c>
       <c r="O19" s="15">
         <f t="shared" si="4"/>
-        <v>125348</v>
+        <v>125349</v>
       </c>
       <c r="P19" s="13">
-        <v>204048</v>
+        <v>204049</v>
       </c>
       <c r="Q19" s="14">
         <f t="shared" si="5"/>
-        <v>0.91784519054302061</v>
+        <v>0.91784968872575479</v>
       </c>
       <c r="R19" s="12">
         <v>205062</v>
@@ -3800,14 +3800,14 @@
       </c>
       <c r="AN26" s="15">
         <f t="shared" si="14"/>
-        <v>7120</v>
+        <v>7121</v>
       </c>
       <c r="AO26" s="13">
-        <v>13743</v>
+        <v>13744</v>
       </c>
       <c r="AP26" s="14">
         <f t="shared" si="15"/>
-        <v>0.85915228807201804</v>
+        <v>0.85921480370092518</v>
       </c>
       <c r="AQ26" s="12">
         <v>16327</v>
@@ -4071,14 +4071,14 @@
       </c>
       <c r="Y28" s="15">
         <f t="shared" si="8"/>
-        <v>140064</v>
+        <v>140065</v>
       </c>
       <c r="Z28" s="13">
-        <v>412811</v>
+        <v>412812</v>
       </c>
       <c r="AA28" s="14">
         <f t="shared" si="9"/>
-        <v>0.9467403918043088</v>
+        <v>0.9467426852034474</v>
       </c>
       <c r="AB28" s="12">
         <v>443892</v>
@@ -4088,14 +4088,14 @@
       </c>
       <c r="AD28" s="15">
         <f t="shared" si="10"/>
-        <v>124929</v>
+        <v>124930</v>
       </c>
       <c r="AE28" s="22">
-        <v>419196</v>
+        <v>419197</v>
       </c>
       <c r="AF28" s="14">
         <f t="shared" si="11"/>
-        <v>0.94436484550296018</v>
+        <v>0.94436709830319088</v>
       </c>
       <c r="AG28" s="12">
         <v>453793</v>
@@ -4105,14 +4105,14 @@
       </c>
       <c r="AI28" s="15">
         <f t="shared" si="12"/>
-        <v>120932</v>
+        <v>120933</v>
       </c>
       <c r="AJ28" s="13">
-        <v>427363</v>
+        <v>427364</v>
       </c>
       <c r="AK28" s="14">
         <f t="shared" si="13"/>
-        <v>0.94175758550704836</v>
+        <v>0.94175978915496716</v>
       </c>
       <c r="AL28" s="12">
         <v>463943</v>
@@ -4681,14 +4681,14 @@
       </c>
       <c r="O32" s="15">
         <f t="shared" si="4"/>
-        <v>166101</v>
+        <v>166102</v>
       </c>
       <c r="P32" s="13">
-        <v>280923</v>
+        <v>280924</v>
       </c>
       <c r="Q32" s="14">
         <f t="shared" si="5"/>
-        <v>0.96753228861718621</v>
+        <v>0.96753573273635263</v>
       </c>
       <c r="R32" s="12">
         <v>274212</v>
@@ -4876,14 +4876,14 @@
       </c>
       <c r="Y33" s="15">
         <f t="shared" si="8"/>
-        <v>206626</v>
+        <v>206627</v>
       </c>
       <c r="Z33" s="13">
-        <v>674450</v>
+        <v>674451</v>
       </c>
       <c r="AA33" s="14">
         <f t="shared" si="9"/>
-        <v>0.98001322280425163</v>
+        <v>0.98001467585966395</v>
       </c>
       <c r="AB33" s="12">
         <v>698869</v>
@@ -4910,14 +4910,14 @@
       </c>
       <c r="AI33" s="15">
         <f t="shared" si="12"/>
-        <v>175973</v>
+        <v>175974</v>
       </c>
       <c r="AJ33" s="13">
-        <v>696872</v>
+        <v>696873</v>
       </c>
       <c r="AK33" s="14">
         <f t="shared" si="13"/>
-        <v>0.97795753172630684</v>
+        <v>0.97795893507947895</v>
       </c>
       <c r="AL33" s="12">
         <v>723682</v>
@@ -4927,14 +4927,14 @@
       </c>
       <c r="AN33" s="15">
         <f t="shared" si="14"/>
-        <v>176022</v>
+        <v>176024</v>
       </c>
       <c r="AO33" s="13">
-        <v>707226</v>
+        <v>707228</v>
       </c>
       <c r="AP33" s="14">
         <f t="shared" si="15"/>
-        <v>0.97726073054186779</v>
+        <v>0.97726349418667313</v>
       </c>
       <c r="AQ33" s="12">
         <v>733311</v>
@@ -4944,14 +4944,14 @@
       </c>
       <c r="AS33" s="15">
         <f t="shared" si="16"/>
-        <v>199523</v>
+        <v>199526</v>
       </c>
       <c r="AT33" s="13">
-        <v>716007</v>
+        <v>716010</v>
       </c>
       <c r="AU33" s="14">
         <f t="shared" si="17"/>
-        <v>0.97640291772522159</v>
+        <v>0.97640700875890307</v>
       </c>
     </row>
     <row r="34" spans="1:47" x14ac:dyDescent="0.3">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="T36" s="15">
         <f t="shared" si="6"/>
-        <v>445770</v>
+        <v>445771</v>
       </c>
       <c r="U36" s="13">
-        <v>1031368</v>
+        <v>1031369</v>
       </c>
       <c r="V36" s="14">
         <f t="shared" si="7"/>
-        <v>0.97773252677851119</v>
+        <v>0.97773347477430594</v>
       </c>
       <c r="W36" s="12">
         <v>1076657</v>
@@ -5359,14 +5359,14 @@
       </c>
       <c r="Y36" s="15">
         <f t="shared" si="8"/>
-        <v>379775</v>
+        <v>379776</v>
       </c>
       <c r="Z36" s="13">
-        <v>1046749</v>
+        <v>1046750</v>
       </c>
       <c r="AA36" s="14">
         <f t="shared" si="9"/>
-        <v>0.97222142242143972</v>
+        <v>0.97222235122234846</v>
       </c>
       <c r="AB36" s="12">
         <v>1094504</v>
@@ -5376,14 +5376,14 @@
       </c>
       <c r="AD36" s="15">
         <f t="shared" si="10"/>
-        <v>319159</v>
+        <v>319160</v>
       </c>
       <c r="AE36" s="22">
-        <v>1061366</v>
+        <v>1061367</v>
       </c>
       <c r="AF36" s="14">
         <f t="shared" si="11"/>
-        <v>0.96972327191129493</v>
+        <v>0.969724185567161</v>
       </c>
       <c r="AG36" s="12">
         <v>1114066</v>
@@ -5393,14 +5393,14 @@
       </c>
       <c r="AI36" s="15">
         <f t="shared" si="12"/>
-        <v>353173</v>
+        <v>353174</v>
       </c>
       <c r="AJ36" s="13">
-        <v>1078135</v>
+        <v>1078136</v>
       </c>
       <c r="AK36" s="14">
         <f t="shared" si="13"/>
-        <v>0.96774787131103546</v>
+        <v>0.9677487689239237</v>
       </c>
       <c r="AL36" s="12">
         <v>1133258</v>
@@ -5410,14 +5410,14 @@
       </c>
       <c r="AN36" s="15">
         <f t="shared" si="14"/>
-        <v>353301</v>
+        <v>353302</v>
       </c>
       <c r="AO36" s="13">
-        <v>1095003</v>
+        <v>1095004</v>
       </c>
       <c r="AP36" s="14">
         <f t="shared" si="15"/>
-        <v>0.96624334441054027</v>
+        <v>0.96624422682213584</v>
       </c>
       <c r="AQ36" s="12">
         <v>1148243</v>
@@ -5427,14 +5427,14 @@
       </c>
       <c r="AS36" s="15">
         <f t="shared" si="16"/>
-        <v>377892</v>
+        <v>377893</v>
       </c>
       <c r="AT36" s="13">
-        <v>1108788</v>
+        <v>1108789</v>
       </c>
       <c r="AU36" s="14">
         <f t="shared" si="17"/>
-        <v>0.96563880641989541</v>
+        <v>0.96563967731569011</v>
       </c>
     </row>
     <row r="37" spans="1:47" x14ac:dyDescent="0.3">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="T37" s="15">
         <f t="shared" si="6"/>
-        <v>196453</v>
+        <v>196454</v>
       </c>
       <c r="U37" s="13">
-        <v>514133</v>
+        <v>514134</v>
       </c>
       <c r="V37" s="14">
         <f t="shared" si="7"/>
-        <v>0.95706246660920813</v>
+        <v>0.95706432811676867</v>
       </c>
       <c r="W37" s="12">
         <v>549345</v>
@@ -5588,14 +5588,14 @@
       </c>
       <c r="AS37" s="15">
         <f t="shared" si="16"/>
-        <v>175711</v>
+        <v>175713</v>
       </c>
       <c r="AT37" s="13">
-        <v>547814</v>
+        <v>547816</v>
       </c>
       <c r="AU37" s="14">
         <f t="shared" si="17"/>
-        <v>0.92847469979576791</v>
+        <v>0.92847808954009647</v>
       </c>
     </row>
     <row r="38" spans="1:47" x14ac:dyDescent="0.3">
@@ -6037,14 +6037,14 @@
       </c>
       <c r="AI40" s="15">
         <f t="shared" si="12"/>
-        <v>89761</v>
+        <v>89762</v>
       </c>
       <c r="AJ40" s="13">
-        <v>232061</v>
+        <v>232062</v>
       </c>
       <c r="AK40" s="14">
         <f t="shared" si="13"/>
-        <v>0.97219091826945236</v>
+        <v>0.97219510764603123</v>
       </c>
       <c r="AL40" s="12">
         <v>242006</v>
@@ -6054,14 +6054,14 @@
       </c>
       <c r="AN40" s="15">
         <f t="shared" si="14"/>
-        <v>94832</v>
+        <v>94833</v>
       </c>
       <c r="AO40" s="13">
-        <v>235071</v>
+        <v>235072</v>
       </c>
       <c r="AP40" s="14">
         <f t="shared" si="15"/>
-        <v>0.97134368569374308</v>
+        <v>0.97134781782269863</v>
       </c>
       <c r="AQ40" s="12">
         <v>245761</v>
@@ -6071,14 +6071,14 @@
       </c>
       <c r="AS40" s="15">
         <f t="shared" si="16"/>
-        <v>108296</v>
+        <v>108297</v>
       </c>
       <c r="AT40" s="13">
-        <v>238386</v>
+        <v>238387</v>
       </c>
       <c r="AU40" s="14">
         <f t="shared" si="17"/>
-        <v>0.96999117028332404</v>
+        <v>0.9699952392771839</v>
       </c>
     </row>
     <row r="41" spans="1:47" x14ac:dyDescent="0.3">
@@ -6113,14 +6113,14 @@
       </c>
       <c r="J41" s="15">
         <f t="shared" si="2"/>
-        <v>440806</v>
+        <v>440811</v>
       </c>
       <c r="K41" s="13">
-        <v>643250</v>
+        <v>643255</v>
       </c>
       <c r="L41" s="14">
         <f t="shared" si="3"/>
-        <v>0.95457230115364866</v>
+        <v>0.95457972107048628</v>
       </c>
       <c r="M41" s="12">
         <v>700632</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="O41" s="15">
         <f t="shared" si="4"/>
-        <v>341601</v>
+        <v>341604</v>
       </c>
       <c r="P41" s="13">
-        <v>665633</v>
+        <v>665636</v>
       </c>
       <c r="Q41" s="14">
         <f t="shared" si="5"/>
-        <v>0.95004652941915302</v>
+        <v>0.95005081126754132</v>
       </c>
       <c r="R41" s="12">
         <v>688720</v>
@@ -6147,14 +6147,14 @@
       </c>
       <c r="T41" s="15">
         <f t="shared" si="6"/>
-        <v>252618</v>
+        <v>252621</v>
       </c>
       <c r="U41" s="13">
-        <v>648491</v>
+        <v>648494</v>
       </c>
       <c r="V41" s="14">
         <f t="shared" si="7"/>
-        <v>0.94158874433732143</v>
+        <v>0.94159310024393073</v>
       </c>
       <c r="W41" s="12">
         <v>702649</v>
@@ -6164,14 +6164,14 @@
       </c>
       <c r="Y41" s="15">
         <f t="shared" si="8"/>
-        <v>224614</v>
+        <v>224617</v>
       </c>
       <c r="Z41" s="13">
-        <v>653179</v>
+        <v>653182</v>
       </c>
       <c r="AA41" s="14">
         <f t="shared" si="9"/>
-        <v>0.92959500404896334</v>
+        <v>0.92959927360602523</v>
       </c>
       <c r="AB41" s="12">
         <v>712131</v>
@@ -6181,14 +6181,14 @@
       </c>
       <c r="AD41" s="15">
         <f t="shared" si="10"/>
-        <v>204664</v>
+        <v>204667</v>
       </c>
       <c r="AE41" s="22">
-        <v>658376</v>
+        <v>658379</v>
       </c>
       <c r="AF41" s="14">
         <f t="shared" si="11"/>
-        <v>0.92451529283235812</v>
+        <v>0.92451950554041318</v>
       </c>
       <c r="AG41" s="12">
         <v>722496</v>
@@ -6198,14 +6198,14 @@
       </c>
       <c r="AI41" s="15">
         <f t="shared" si="12"/>
-        <v>206310</v>
+        <v>206312</v>
       </c>
       <c r="AJ41" s="13">
-        <v>665054</v>
+        <v>665056</v>
       </c>
       <c r="AK41" s="14">
         <f t="shared" si="13"/>
-        <v>0.92049506156435468</v>
+        <v>0.92049782974577021</v>
       </c>
       <c r="AL41" s="12">
         <v>737038</v>
@@ -6215,14 +6215,14 @@
       </c>
       <c r="AN41" s="15">
         <f t="shared" si="14"/>
-        <v>213614</v>
+        <v>213616</v>
       </c>
       <c r="AO41" s="13">
-        <v>675129</v>
+        <v>675131</v>
       </c>
       <c r="AP41" s="14">
         <f t="shared" si="15"/>
-        <v>0.91600297406646602</v>
+        <v>0.91600568763075985</v>
       </c>
       <c r="AQ41" s="12">
         <v>750910</v>
@@ -6232,14 +6232,14 @@
       </c>
       <c r="AS41" s="15">
         <f t="shared" si="16"/>
-        <v>230893</v>
+        <v>230895</v>
       </c>
       <c r="AT41" s="13">
-        <v>684750</v>
+        <v>684752</v>
       </c>
       <c r="AU41" s="14">
         <f t="shared" si="17"/>
-        <v>0.91189356913611486</v>
+        <v>0.91189623257114705</v>
       </c>
     </row>
     <row r="42" spans="1:47" x14ac:dyDescent="0.3">
@@ -6452,14 +6452,14 @@
       </c>
       <c r="O43" s="15">
         <f t="shared" si="4"/>
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="P43" s="13">
-        <v>3235</v>
+        <v>3236</v>
       </c>
       <c r="Q43" s="14">
         <f t="shared" si="5"/>
-        <v>0.82778915046059365</v>
+        <v>0.82804503582395084</v>
       </c>
       <c r="R43" s="12">
         <v>3837</v>
@@ -6469,14 +6469,14 @@
       </c>
       <c r="T43" s="15">
         <f t="shared" si="6"/>
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="U43" s="13">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="V43" s="14">
         <f t="shared" si="7"/>
-        <v>0.82616627573625223</v>
+        <v>0.82642689601250974</v>
       </c>
       <c r="W43" s="12">
         <v>3971</v>
@@ -6486,14 +6486,14 @@
       </c>
       <c r="Y43" s="15">
         <f t="shared" si="8"/>
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="Z43" s="13">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="AA43" s="14">
         <f t="shared" si="9"/>
-        <v>0.81289347771342235</v>
+        <v>0.81314530345001257</v>
       </c>
       <c r="AB43" s="12">
         <v>4016</v>
@@ -6503,14 +6503,14 @@
       </c>
       <c r="AD43" s="15">
         <f t="shared" si="10"/>
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="AE43" s="22">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="AF43" s="14">
         <f t="shared" si="11"/>
-        <v>0.8072709163346613</v>
+        <v>0.8075199203187251</v>
       </c>
       <c r="AG43" s="12">
         <v>4109</v>
@@ -6520,14 +6520,14 @@
       </c>
       <c r="AI43" s="15">
         <f t="shared" si="12"/>
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="AJ43" s="13">
-        <v>3298</v>
+        <v>3300</v>
       </c>
       <c r="AK43" s="14">
         <f t="shared" si="13"/>
-        <v>0.80262837673399856</v>
+        <v>0.80311511316622053</v>
       </c>
       <c r="AL43" s="12">
         <v>4182</v>
@@ -6537,14 +6537,14 @@
       </c>
       <c r="AN43" s="15">
         <f t="shared" si="14"/>
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="AO43" s="13">
-        <v>3337</v>
+        <v>3339</v>
       </c>
       <c r="AP43" s="14">
         <f t="shared" si="15"/>
-        <v>0.79794356767097085</v>
+        <v>0.79842180774748928</v>
       </c>
       <c r="AQ43" s="12">
         <v>4246</v>
@@ -6554,14 +6554,14 @@
       </c>
       <c r="AS43" s="15">
         <f t="shared" si="16"/>
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="AT43" s="13">
-        <v>3371</v>
+        <v>3373</v>
       </c>
       <c r="AU43" s="14">
         <f t="shared" si="17"/>
-        <v>0.79392369288742348</v>
+        <v>0.79439472444653791</v>
       </c>
     </row>
     <row r="44" spans="1:47" x14ac:dyDescent="0.3">
@@ -7223,15 +7223,15 @@
       </c>
       <c r="J48" s="18">
         <f t="shared" si="2"/>
-        <v>4422337</v>
+        <v>4422342</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>7216096</v>
+        <v>7216101</v>
       </c>
       <c r="L48" s="19">
         <f t="shared" si="3"/>
-        <v>0.96507455556473898</v>
+        <v>0.96507522426049608</v>
       </c>
       <c r="M48" s="17">
         <f>SUM(M10:M47)</f>
@@ -7243,15 +7243,15 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" si="4"/>
-        <v>3706442</v>
+        <v>3706450</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>7574225</v>
+        <v>7574233</v>
       </c>
       <c r="Q48" s="19">
         <f t="shared" si="5"/>
-        <v>0.96646538736514831</v>
+        <v>0.96646640815910401</v>
       </c>
       <c r="R48" s="17">
         <f>SUM(R10:R47)</f>
@@ -7263,15 +7263,15 @@
       </c>
       <c r="T48" s="18">
         <f t="shared" si="6"/>
-        <v>2999230</v>
+        <v>2999236</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>7326954</v>
+        <v>7326960</v>
       </c>
       <c r="V48" s="19">
         <f t="shared" si="7"/>
-        <v>0.95806344179816316</v>
+        <v>0.95806422635074129</v>
       </c>
       <c r="W48" s="17">
         <f>SUM(W10:W47)</f>
@@ -7283,15 +7283,15 @@
       </c>
       <c r="Y48" s="18">
         <f t="shared" si="8"/>
-        <v>2552777</v>
+        <v>2552786</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>7437213</v>
+        <v>7437222</v>
       </c>
       <c r="AA48" s="19">
         <f t="shared" si="9"/>
-        <v>0.94834226562768975</v>
+        <v>0.94834341324580829</v>
       </c>
       <c r="AB48" s="17">
         <f>SUM(AB10:AB47)</f>
@@ -7303,15 +7303,15 @@
       </c>
       <c r="AD48" s="18">
         <f t="shared" si="10"/>
-        <v>2124172</v>
+        <v>2124179</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>7529921</v>
+        <v>7529928</v>
       </c>
       <c r="AF48" s="19">
         <f t="shared" si="11"/>
-        <v>0.94467922973585339</v>
+        <v>0.94468010793292978</v>
       </c>
       <c r="AG48" s="17">
         <f>SUM(AG10:AG47)</f>
@@ -7323,15 +7323,15 @@
       </c>
       <c r="AI48" s="18">
         <f t="shared" si="12"/>
-        <v>2280265</v>
+        <v>2280273</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7660839</v>
+        <v>7660847</v>
       </c>
       <c r="AK48" s="19">
         <f t="shared" si="13"/>
-        <v>0.94075339463033547</v>
+        <v>0.94075437703280562</v>
       </c>
       <c r="AL48" s="17">
         <f>SUM(AL10:AL47)</f>
@@ -7343,15 +7343,15 @@
       </c>
       <c r="AN48" s="18">
         <f t="shared" si="14"/>
-        <v>2359990</v>
+        <v>2359999</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>7795790</v>
+        <v>7795799</v>
       </c>
       <c r="AP48" s="19">
         <f t="shared" si="15"/>
-        <v>0.937930116789642</v>
+        <v>0.93793119960114035</v>
       </c>
       <c r="AQ48" s="17">
         <f>SUM(AQ10:AQ47)</f>
@@ -7363,15 +7363,15 @@
       </c>
       <c r="AS48" s="18">
         <f t="shared" si="16"/>
-        <v>2655166</v>
+        <v>2655180</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>7915075</v>
+        <v>7915089</v>
       </c>
       <c r="AU48" s="19">
         <f t="shared" si="17"/>
-        <v>0.93607125569428096</v>
+        <v>0.93607291139527937</v>
       </c>
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.3">
